--- a/outputs/Block4_Largest_Adjustments_v12.xlsx
+++ b/outputs/Block4_Largest_Adjustments_v12.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="47">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="100" uniqueCount="48">
   <si>
     <t>Variable</t>
   </si>
@@ -106,55 +106,58 @@
     <t>Model Stability</t>
   </si>
   <si>
+    <t>RSenSafResH (&gt;10%)</t>
+  </si>
+  <si>
     <t>RHouSafResH (&gt;10%)</t>
   </si>
   <si>
     <t>DHouSafResH (&gt;5%&lt;=10%)</t>
   </si>
   <si>
-    <t>RSenSafResH (&gt;10%)</t>
-  </si>
-  <si>
     <t>DSenSafResH (&gt;10%)</t>
   </si>
   <si>
-    <t>RHouLeanResH  (&gt;1&lt;=5%)</t>
-  </si>
-  <si>
-    <t>RHouLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RSenLikResH (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouLikResLD (&gt;5%&lt;=10%)</t>
-  </si>
-  <si>
-    <t>RHouSafResLD (&gt;10%)</t>
-  </si>
-  <si>
-    <t>RSenTiltResLD (&lt;=1%)</t>
+    <t>RHouTiltResLD (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>RHouTiltResH (&lt;=1%)</t>
+  </si>
+  <si>
+    <t>DHouLikResLR (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DSenLikResH (&gt;5%&lt;=10%)</t>
+  </si>
+  <si>
+    <t>DHouLeanResLR  (&gt;1&lt;=5%)</t>
+  </si>
+  <si>
+    <t>RSenSafResLD (&gt;10%)</t>
+  </si>
+  <si>
+    <t>Senate Buckets</t>
   </si>
   <si>
     <t>House Buckets</t>
   </si>
   <si>
-    <t>Senate Buckets</t>
-  </si>
-  <si>
     <t>ML Predicted</t>
   </si>
   <si>
     <t>Integer</t>
   </si>
   <si>
+    <t>High sensitivity</t>
+  </si>
+  <si>
+    <t>Low sensitivity</t>
+  </si>
+  <si>
+    <t>Moderate-low sensitivity</t>
+  </si>
+  <si>
     <t>Moderate sensitivity</t>
-  </si>
-  <si>
-    <t>High sensitivity</t>
-  </si>
-  <si>
-    <t>Very high sensitivity</t>
   </si>
 </sst>
 </file>
@@ -615,79 +618,79 @@
         <v>40</v>
       </c>
       <c r="C2">
-        <v>173.296</v>
+        <v>10.028</v>
       </c>
       <c r="D2">
-        <v>175.72</v>
+        <v>11.468</v>
       </c>
       <c r="E2">
-        <v>182.3239848953666</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="F2">
-        <v>172.6</v>
+        <v>11.6</v>
       </c>
       <c r="G2">
-        <v>174.4659250965879</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="J2" t="s">
         <v>4</v>
       </c>
       <c r="K2">
-        <v>182.3239848953666</v>
+        <v>13.28203815275881</v>
       </c>
       <c r="L2">
-        <v>24.70132137894479</v>
+        <v>3.050242274051084</v>
       </c>
       <c r="M2">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N2">
-        <v>18.7</v>
+        <v>5.6</v>
       </c>
       <c r="O2" t="s">
         <v>42</v>
       </c>
       <c r="P2">
-        <v>170.7162008332492</v>
+        <v>15.15860750983988</v>
       </c>
       <c r="Q2">
-        <v>0.9363343003457338</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R2">
-        <v>171</v>
+        <v>15</v>
       </c>
       <c r="S2" t="s">
         <v>43</v>
       </c>
       <c r="T2">
-        <v>-11.60778406211739</v>
+        <v>1.876569357081072</v>
       </c>
       <c r="U2">
-        <v>0.2837991667507822</v>
+        <v>-0.158607509839884</v>
       </c>
       <c r="V2" t="s">
         <v>6</v>
       </c>
       <c r="W2">
-        <v>174.4659250965879</v>
+        <v>10.70483610671818</v>
       </c>
       <c r="X2">
-        <v>7.858059798778754</v>
+        <v>2.577202046040632</v>
       </c>
       <c r="Y2">
-        <v>11.32398489536661</v>
+        <v>1.717961847241188</v>
       </c>
       <c r="Z2">
-        <v>0.3181230541568072</v>
+        <v>0.8449171621432557</v>
       </c>
       <c r="AA2">
-        <v>0.4584364019092145</v>
+        <v>0.5632214404266095</v>
       </c>
       <c r="AB2">
-        <v>1.320926276948919</v>
+        <v>0.544686120366265</v>
       </c>
       <c r="AC2">
-        <v>69.26484290771914</v>
+        <v>47.41063290551929</v>
       </c>
       <c r="AD2" t="s">
         <v>44</v>
@@ -698,82 +701,82 @@
         <v>31</v>
       </c>
       <c r="B3" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C3">
-        <v>173.312</v>
+        <v>172.1</v>
       </c>
       <c r="D3">
-        <v>170.552</v>
+        <v>175.156</v>
       </c>
       <c r="E3">
-        <v>176.0063243272117</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="F3">
-        <v>169.2</v>
+        <v>172.6</v>
       </c>
       <c r="G3">
-        <v>171.9799070682415</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="J3" t="s">
         <v>4</v>
       </c>
       <c r="K3">
-        <v>176.0063243272117</v>
+        <v>175.5898630732044</v>
       </c>
       <c r="L3">
-        <v>4.764861070548267</v>
+        <v>24.70132137894479</v>
       </c>
       <c r="M3">
         <v>5.24749619700716</v>
       </c>
       <c r="N3">
-        <v>13.2</v>
+        <v>18.7</v>
       </c>
       <c r="O3" t="s">
         <v>42</v>
       </c>
       <c r="P3">
-        <v>181.3185762509099</v>
+        <v>173.8081494148196</v>
       </c>
       <c r="Q3">
-        <v>1.030182165010288</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R3">
-        <v>181</v>
+        <v>174</v>
       </c>
       <c r="S3" t="s">
         <v>43</v>
       </c>
       <c r="T3">
-        <v>5.31225192369817</v>
+        <v>-1.781713658384717</v>
       </c>
       <c r="U3">
-        <v>-0.3185762509098993</v>
+        <v>0.1918505851803616</v>
       </c>
       <c r="V3" t="s">
         <v>6</v>
       </c>
       <c r="W3">
-        <v>171.9799070682415</v>
+        <v>173.5749550722659</v>
       </c>
       <c r="X3">
-        <v>4.026417258970184</v>
+        <v>2.014908000938448</v>
       </c>
       <c r="Y3">
-        <v>4.993675672788271</v>
+        <v>1.589863073204356</v>
       </c>
       <c r="Z3">
-        <v>0.845023013127828</v>
+        <v>0.08157085890376452</v>
       </c>
       <c r="AA3">
-        <v>1.04802125368446</v>
+        <v>0.06436348277948976</v>
       </c>
       <c r="AB3">
-        <v>0.3609743235263839</v>
+        <v>1.320926276948919</v>
       </c>
       <c r="AC3">
-        <v>40.00873433552916</v>
+        <v>92.72349650896915</v>
       </c>
       <c r="AD3" t="s">
         <v>45</v>
@@ -787,82 +790,82 @@
         <v>41</v>
       </c>
       <c r="C4">
-        <v>10.056</v>
+        <v>172.984</v>
       </c>
       <c r="D4">
-        <v>11.612</v>
+        <v>170.488</v>
       </c>
       <c r="E4">
-        <v>12.72721886527684</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="F4">
-        <v>11.6</v>
+        <v>169.2</v>
       </c>
       <c r="G4">
-        <v>10.78735901531492</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="J4" t="s">
         <v>4</v>
       </c>
       <c r="K4">
-        <v>12.72721886527684</v>
+        <v>172.6467820636017</v>
       </c>
       <c r="L4">
-        <v>3.050242274051084</v>
+        <v>4.764861070548267</v>
       </c>
       <c r="M4">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N4">
-        <v>5.6</v>
+        <v>13.2</v>
       </c>
       <c r="O4" t="s">
         <v>42</v>
       </c>
       <c r="P4">
-        <v>14.76027887619046</v>
+        <v>174.4769462223457</v>
       </c>
       <c r="Q4">
-        <v>1.159741105455516</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R4">
-        <v>15</v>
+        <v>174</v>
       </c>
       <c r="S4" t="s">
         <v>43</v>
       </c>
       <c r="T4">
-        <v>2.033060010913617</v>
+        <v>1.830164158743969</v>
       </c>
       <c r="U4">
-        <v>0.2397211238095416</v>
+        <v>-0.4769462223457026</v>
       </c>
       <c r="V4" t="s">
         <v>6</v>
       </c>
       <c r="W4">
-        <v>10.78735901531492</v>
+        <v>171.7793246530184</v>
       </c>
       <c r="X4">
-        <v>1.939859849961922</v>
+        <v>0.8674574105832846</v>
       </c>
       <c r="Y4">
-        <v>2.272781134723159</v>
+        <v>1.353217936398266</v>
       </c>
       <c r="Z4">
-        <v>0.6359691052952189</v>
+        <v>0.1820530331818197</v>
       </c>
       <c r="AA4">
-        <v>0.7451149549850793</v>
+        <v>0.2839994527358924</v>
       </c>
       <c r="AB4">
-        <v>0.544686120366265</v>
+        <v>0.3609743235263839</v>
       </c>
       <c r="AC4">
-        <v>50.95791180581695</v>
+        <v>80.43391422492162</v>
       </c>
       <c r="AD4" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="5" spans="1:30">
@@ -870,28 +873,28 @@
         <v>33</v>
       </c>
       <c r="B5" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C5">
-        <v>13.152</v>
+        <v>13.232</v>
       </c>
       <c r="D5">
-        <v>12.22</v>
+        <v>12.328</v>
       </c>
       <c r="E5">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="F5">
         <v>12.4</v>
       </c>
       <c r="G5">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="J5" t="s">
         <v>4</v>
       </c>
       <c r="K5">
-        <v>11.17487741647244</v>
+        <v>11.23658004704028</v>
       </c>
       <c r="L5">
         <v>2.351026032651849</v>
@@ -906,49 +909,49 @@
         <v>42</v>
       </c>
       <c r="P5">
-        <v>9.132471991736034</v>
+        <v>9.674452691001546</v>
       </c>
       <c r="Q5">
-        <v>0.8172324090351291</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R5">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="S5" t="s">
         <v>43</v>
       </c>
       <c r="T5">
-        <v>-2.04240542473641</v>
+        <v>-1.562127356038731</v>
       </c>
       <c r="U5">
-        <v>-0.1324719917360344</v>
+        <v>0.3255473089984537</v>
       </c>
       <c r="V5" t="s">
         <v>6</v>
       </c>
       <c r="W5">
-        <v>12.71393663092962</v>
+        <v>12.8070973330047</v>
       </c>
       <c r="X5">
-        <v>1.539059214457176</v>
+        <v>1.570517285964419</v>
       </c>
       <c r="Y5">
-        <v>2.174877416472444</v>
+        <v>1.236580047040277</v>
       </c>
       <c r="Z5">
-        <v>0.6546329955866917</v>
+        <v>0.6680135669076143</v>
       </c>
       <c r="AA5">
-        <v>0.9250758546553748</v>
+        <v>0.5259746297430284</v>
       </c>
       <c r="AB5">
         <v>0.6530627868477359</v>
       </c>
       <c r="AC5">
-        <v>47.27029992542463</v>
+        <v>53.88597538332969</v>
       </c>
       <c r="AD5" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" spans="1:30">
@@ -956,85 +959,85 @@
         <v>34</v>
       </c>
       <c r="B6" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C6">
-        <v>13.488</v>
+        <v>1.832</v>
       </c>
       <c r="D6">
-        <v>12.544</v>
+        <v>1.772</v>
       </c>
       <c r="E6">
-        <v>15.02106749310035</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="F6">
-        <v>11.8</v>
+        <v>1.6</v>
       </c>
       <c r="G6">
-        <v>13.03238560594928</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="J6" t="s">
         <v>4</v>
       </c>
       <c r="K6">
-        <v>15.02106749310035</v>
+        <v>2.554644495322226</v>
       </c>
       <c r="L6">
-        <v>3.125306797245826</v>
+        <v>1.198624596172324</v>
       </c>
       <c r="M6">
         <v>5.24749619700716</v>
       </c>
       <c r="N6">
-        <v>4.8</v>
+        <v>1.6</v>
       </c>
       <c r="O6" t="s">
         <v>42</v>
       </c>
       <c r="P6">
-        <v>14.06474072159816</v>
+        <v>2.528722469358031</v>
       </c>
       <c r="Q6">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R6">
-        <v>14</v>
+        <v>2</v>
       </c>
       <c r="S6" t="s">
         <v>43</v>
       </c>
       <c r="T6">
-        <v>-0.956326771502189</v>
+        <v>-0.02592202596419435</v>
       </c>
       <c r="U6">
-        <v>-0.06474072159816124</v>
+        <v>-0.5287224693580312</v>
       </c>
       <c r="V6" t="s">
         <v>6</v>
       </c>
       <c r="W6">
-        <v>13.03238560594928</v>
+        <v>1.803041458005251</v>
       </c>
       <c r="X6">
-        <v>1.988681887151071</v>
+        <v>0.7516030373169746</v>
       </c>
       <c r="Y6">
-        <v>1.02106749310035</v>
+        <v>0.5546444953222256</v>
       </c>
       <c r="Z6">
-        <v>0.6363157335156967</v>
+        <v>0.627054575483547</v>
       </c>
       <c r="AA6">
-        <v>0.3267095230459183</v>
+        <v>0.4627341179994319</v>
       </c>
       <c r="AB6">
-        <v>0.6511055827595471</v>
+        <v>0.7491403726077025</v>
       </c>
       <c r="AC6">
-        <v>58.9810747875693</v>
+        <v>56.57842736664286</v>
       </c>
       <c r="AD6" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
     </row>
     <row r="7" spans="1:30">
@@ -1042,85 +1045,85 @@
         <v>35</v>
       </c>
       <c r="B7" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C7">
-        <v>15.112</v>
+        <v>3.692</v>
       </c>
       <c r="D7">
-        <v>15.028</v>
+        <v>3.192</v>
       </c>
       <c r="E7">
-        <v>17.90152433308469</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="F7">
-        <v>14.2</v>
+        <v>3</v>
       </c>
       <c r="G7">
-        <v>15.07145804120735</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="J7" t="s">
         <v>4</v>
       </c>
       <c r="K7">
-        <v>17.90152433308469</v>
+        <v>3.475459163737268</v>
       </c>
       <c r="L7">
-        <v>6.129350049043507</v>
+        <v>0.887818750560327</v>
       </c>
       <c r="M7">
         <v>5.24749619700716</v>
       </c>
       <c r="N7">
-        <v>6.3</v>
+        <v>2.5</v>
       </c>
       <c r="O7" t="s">
         <v>42</v>
       </c>
       <c r="P7">
-        <v>16.76181126154098</v>
+        <v>3.440193613933819</v>
       </c>
       <c r="Q7">
-        <v>0.9363343003457338</v>
+        <v>0.9898529811049405</v>
       </c>
       <c r="R7">
-        <v>17</v>
+        <v>3</v>
       </c>
       <c r="S7" t="s">
         <v>43</v>
       </c>
       <c r="T7">
-        <v>-1.13971307154371</v>
+        <v>-0.03526554980344976</v>
       </c>
       <c r="U7">
-        <v>0.2381887384590158</v>
+        <v>-0.4401936139338187</v>
       </c>
       <c r="V7" t="s">
         <v>6</v>
       </c>
       <c r="W7">
-        <v>15.07145804120735</v>
+        <v>3.450678816710424</v>
       </c>
       <c r="X7">
-        <v>2.830066291877342</v>
+        <v>0.0247803470268444</v>
       </c>
       <c r="Y7">
-        <v>0.9015243330846943</v>
+        <v>0.4754591637372685</v>
       </c>
       <c r="Z7">
-        <v>0.4617237177241946</v>
+        <v>0.02791149320872625</v>
       </c>
       <c r="AA7">
-        <v>0.1470831859611899</v>
+        <v>0.5355362943587225</v>
       </c>
       <c r="AB7">
-        <v>0.972912706197382</v>
+        <v>0.3551275002241308</v>
       </c>
       <c r="AC7">
-        <v>70.35618198382974</v>
+        <v>81.41748166151876</v>
       </c>
       <c r="AD7" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
     <row r="8" spans="1:30">
@@ -1131,79 +1134,79 @@
         <v>41</v>
       </c>
       <c r="C8">
-        <v>1.148</v>
+        <v>3.184</v>
       </c>
       <c r="D8">
-        <v>1.224</v>
+        <v>4.004</v>
       </c>
       <c r="E8">
-        <v>2.2065080011038</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="F8">
-        <v>1</v>
+        <v>5.8</v>
       </c>
       <c r="G8">
-        <v>1.183721905632348</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="J8" t="s">
         <v>4</v>
       </c>
       <c r="K8">
-        <v>2.2065080011038</v>
+        <v>1.550377686812013</v>
       </c>
       <c r="L8">
-        <v>0.8500971208676269</v>
+        <v>7.059923274159115</v>
       </c>
       <c r="M8">
-        <v>1.038416113387647</v>
+        <v>5.24749619700716</v>
       </c>
       <c r="N8">
-        <v>0.5</v>
+        <v>7.6</v>
       </c>
       <c r="O8" t="s">
         <v>42</v>
       </c>
       <c r="P8">
-        <v>2.558978028396561</v>
+        <v>1.566812662552681</v>
       </c>
       <c r="Q8">
-        <v>1.159741105455516</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R8">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="S8" t="s">
         <v>43</v>
       </c>
       <c r="T8">
-        <v>0.3524700272927612</v>
+        <v>0.01643497574066832</v>
       </c>
       <c r="U8">
-        <v>0.4410219716034391</v>
+        <v>0.433187337447319</v>
       </c>
       <c r="V8" t="s">
         <v>6</v>
       </c>
       <c r="W8">
-        <v>1.183721905632348</v>
+        <v>3.579766740594905</v>
       </c>
       <c r="X8">
-        <v>1.022786095471451</v>
+        <v>2.029389053782892</v>
       </c>
       <c r="Y8">
-        <v>0.7934919988962004</v>
+        <v>0.4496223131879873</v>
       </c>
       <c r="Z8">
-        <v>1.203140288756154</v>
+        <v>0.2874519984106493</v>
       </c>
       <c r="AA8">
-        <v>0.933413347037743</v>
+        <v>0.06368657218042365</v>
       </c>
       <c r="AB8">
-        <v>1.700194241735254</v>
+        <v>0.9289372729156731</v>
       </c>
       <c r="AC8">
-        <v>32.99758334560023</v>
+        <v>81.12864354622022</v>
       </c>
       <c r="AD8" t="s">
         <v>46</v>
@@ -1217,82 +1220,82 @@
         <v>40</v>
       </c>
       <c r="C9">
-        <v>7.252</v>
+        <v>1.9</v>
       </c>
       <c r="D9">
-        <v>5.608</v>
+        <v>1.54</v>
       </c>
       <c r="E9">
-        <v>4.766317009415515</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="F9">
-        <v>5.8</v>
+        <v>1.6</v>
       </c>
       <c r="G9">
-        <v>6.458535949343873</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="J9" t="s">
         <v>4</v>
       </c>
       <c r="K9">
-        <v>4.766317009415515</v>
+        <v>1.430889012604439</v>
       </c>
       <c r="L9">
-        <v>3.997862832988686</v>
+        <v>1.157976831184469</v>
       </c>
       <c r="M9">
-        <v>5.24749619700716</v>
+        <v>1.038416113387647</v>
       </c>
       <c r="N9">
-        <v>6.7</v>
+        <v>1.4</v>
       </c>
       <c r="O9" t="s">
         <v>42</v>
       </c>
       <c r="P9">
-        <v>4.462866102237046</v>
+        <v>1.231964530182992</v>
       </c>
       <c r="Q9">
-        <v>0.9363343003457338</v>
+        <v>0.8609783982760665</v>
       </c>
       <c r="R9">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="S9" t="s">
         <v>43</v>
       </c>
       <c r="T9">
-        <v>-0.3034509071784681</v>
+        <v>-0.1989244824214469</v>
       </c>
       <c r="U9">
-        <v>-0.4628661022370464</v>
+        <v>-0.2319645301829925</v>
       </c>
       <c r="V9" t="s">
         <v>6</v>
       </c>
       <c r="W9">
-        <v>6.458535949343873</v>
+        <v>1.730790973320455</v>
       </c>
       <c r="X9">
-        <v>1.692218939928359</v>
+        <v>0.2999019607160154</v>
       </c>
       <c r="Y9">
-        <v>0.7663170094155145</v>
+        <v>0.4308890126044393</v>
       </c>
       <c r="Z9">
-        <v>0.4232808904709982</v>
+        <v>0.2589878766479743</v>
       </c>
       <c r="AA9">
-        <v>0.1916816662873444</v>
+        <v>0.3721050378561482</v>
       </c>
       <c r="AB9">
-        <v>0.5966959452221919</v>
+        <v>0.8271263079889064</v>
       </c>
       <c r="AC9">
-        <v>71.01911200459742</v>
+        <v>74.18717584194117</v>
       </c>
       <c r="AD9" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="10" spans="1:30">
@@ -1300,85 +1303,85 @@
         <v>38</v>
       </c>
       <c r="B10" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="C10">
-        <v>5.232</v>
+        <v>3.54</v>
       </c>
       <c r="D10">
-        <v>4.208</v>
+        <v>4.812</v>
       </c>
       <c r="E10">
-        <v>3.696547591818899</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="F10">
-        <v>4.4</v>
+        <v>5</v>
       </c>
       <c r="G10">
-        <v>4.737774216622949</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="J10" t="s">
         <v>4</v>
       </c>
       <c r="K10">
-        <v>3.696547591818899</v>
+        <v>5.586198698614951</v>
       </c>
       <c r="L10">
-        <v>2.858585552684069</v>
+        <v>2.262338789582505</v>
       </c>
       <c r="M10">
         <v>5.24749619700716</v>
       </c>
       <c r="N10">
-        <v>4.1</v>
+        <v>5</v>
       </c>
       <c r="O10" t="s">
         <v>42</v>
       </c>
       <c r="P10">
-        <v>3.461204303080457</v>
+        <v>5.645415907992541</v>
       </c>
       <c r="Q10">
-        <v>0.9363343003457338</v>
+        <v>1.010600627112006</v>
       </c>
       <c r="R10">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="S10" t="s">
         <v>43</v>
       </c>
       <c r="T10">
-        <v>-0.2353432887384428</v>
+        <v>0.05921720937758934</v>
       </c>
       <c r="U10">
-        <v>-0.4612043030804567</v>
+        <v>0.3545840920074594</v>
       </c>
       <c r="V10" t="s">
         <v>6</v>
       </c>
       <c r="W10">
-        <v>4.737774216622949</v>
+        <v>4.153921090288683</v>
       </c>
       <c r="X10">
-        <v>1.041226624804049</v>
+        <v>1.432277608326268</v>
       </c>
       <c r="Y10">
-        <v>0.6965475918188995</v>
+        <v>0.4138013013850488</v>
       </c>
       <c r="Z10">
-        <v>0.3642453953586904</v>
+        <v>0.633095986737947</v>
       </c>
       <c r="AA10">
-        <v>0.2436686182664276</v>
+        <v>0.1829086356519627</v>
       </c>
       <c r="AB10">
-        <v>0.6972159884595291</v>
+        <v>0.452467757916501</v>
       </c>
       <c r="AC10">
-        <v>72.46666497041721</v>
+        <v>62.15552874778314</v>
       </c>
       <c r="AD10" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11" spans="1:30">
@@ -1386,28 +1389,28 @@
         <v>39</v>
       </c>
       <c r="B11" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C11">
-        <v>0.656</v>
+        <v>0.632</v>
       </c>
       <c r="D11">
-        <v>0.384</v>
+        <v>0.416</v>
       </c>
       <c r="E11">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="F11">
         <v>0.4</v>
       </c>
       <c r="G11">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="J11" t="s">
         <v>4</v>
       </c>
       <c r="K11">
-        <v>0.4366083165842541</v>
+        <v>0.6558051063869967</v>
       </c>
       <c r="L11">
         <v>0.7620693762924241</v>
@@ -1422,10 +1425,10 @@
         <v>42</v>
       </c>
       <c r="P11">
-        <v>0.5063526117264946</v>
+        <v>0.7484613503089816</v>
       </c>
       <c r="Q11">
-        <v>1.159741105455516</v>
+        <v>1.141286249557361</v>
       </c>
       <c r="R11">
         <v>1</v>
@@ -1434,37 +1437,37 @@
         <v>43</v>
       </c>
       <c r="T11">
-        <v>0.06974429514224045</v>
+        <v>0.0926562439219849</v>
       </c>
       <c r="U11">
-        <v>0.4936473882735054</v>
+        <v>0.2515386496910184</v>
       </c>
       <c r="V11" t="s">
         <v>6</v>
       </c>
       <c r="W11">
-        <v>0.5281531798421215</v>
+        <v>0.530474583992273</v>
       </c>
       <c r="X11">
-        <v>0.09154486325786737</v>
+        <v>0.1253305223947238</v>
       </c>
       <c r="Y11">
-        <v>0.5633916834157459</v>
+        <v>0.3441948936130033</v>
       </c>
       <c r="Z11">
-        <v>0.1201266788901112</v>
+        <v>0.1644607778421363</v>
       </c>
       <c r="AA11">
-        <v>0.7392918557582336</v>
+        <v>0.4516582142265844</v>
       </c>
       <c r="AB11">
         <v>0.95258672036553</v>
       </c>
       <c r="AC11">
-        <v>71.40270081666996</v>
+        <v>76.72213858724069</v>
       </c>
       <c r="AD11" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
     </row>
   </sheetData>
